--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/132.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/132.xlsx
@@ -426,13 +426,13 @@
         <v>-17.35886014817108</v>
       </c>
       <c r="E2">
-        <v>-14.82729922616017</v>
+        <v>-13.91329014634802</v>
       </c>
       <c r="F2">
-        <v>4.085838401953371</v>
+        <v>4.750565137799446</v>
       </c>
       <c r="G2">
-        <v>-9.269273748621133</v>
+        <v>-5.719312866495394</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.25689534136631</v>
       </c>
       <c r="E3">
-        <v>-16.03913698450879</v>
+        <v>-13.74114926389444</v>
       </c>
       <c r="F3">
-        <v>3.927621884753471</v>
+        <v>4.488030656830198</v>
       </c>
       <c r="G3">
-        <v>-8.166156937843963</v>
+        <v>-5.259852182736563</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.11311367774212</v>
       </c>
       <c r="E4">
-        <v>-15.81966902020105</v>
+        <v>-15.16736045329217</v>
       </c>
       <c r="F4">
-        <v>4.202255500008008</v>
+        <v>4.662938777196509</v>
       </c>
       <c r="G4">
-        <v>-7.963270154469729</v>
+        <v>-5.244991143810775</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.94101067396087</v>
       </c>
       <c r="E5">
-        <v>-16.91824058666982</v>
+        <v>-16.34758040611923</v>
       </c>
       <c r="F5">
-        <v>4.53170881324501</v>
+        <v>4.392468536508441</v>
       </c>
       <c r="G5">
-        <v>-7.411114195611305</v>
+        <v>-4.421602188919863</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.72738389603469</v>
       </c>
       <c r="E6">
-        <v>-17.20562660414459</v>
+        <v>-17.79047902223522</v>
       </c>
       <c r="F6">
-        <v>3.899931219212689</v>
+        <v>4.762026429184579</v>
       </c>
       <c r="G6">
-        <v>-6.441604381708042</v>
+        <v>-3.895715408915557</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.48132533498179</v>
       </c>
       <c r="E7">
-        <v>-18.43295174359945</v>
+        <v>-17.7468335897493</v>
       </c>
       <c r="F7">
-        <v>4.28377016591309</v>
+        <v>4.685117486039062</v>
       </c>
       <c r="G7">
-        <v>-7.013881836354156</v>
+        <v>-2.888174047857146</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.18764954574747</v>
       </c>
       <c r="E8">
-        <v>-18.75760710215735</v>
+        <v>-18.54595075551284</v>
       </c>
       <c r="F8">
-        <v>4.618298057859643</v>
+        <v>4.870226122603445</v>
       </c>
       <c r="G8">
-        <v>-6.223436120124531</v>
+        <v>-3.108557064406429</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.84176030611123</v>
       </c>
       <c r="E9">
-        <v>-19.40800012456099</v>
+        <v>-18.86334697023645</v>
       </c>
       <c r="F9">
-        <v>4.361898465875528</v>
+        <v>4.53100470095263</v>
       </c>
       <c r="G9">
-        <v>-5.547475689733983</v>
+        <v>-2.052923408299026</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.43537724055194</v>
       </c>
       <c r="E10">
-        <v>-20.74258217088751</v>
+        <v>-20.1268002753245</v>
       </c>
       <c r="F10">
-        <v>4.23384611928117</v>
+        <v>4.916530203685132</v>
       </c>
       <c r="G10">
-        <v>-5.02230067702062</v>
+        <v>-1.538789064959131</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.95635177291959</v>
       </c>
       <c r="E11">
-        <v>-22.51833268351529</v>
+        <v>-21.17992407665228</v>
       </c>
       <c r="F11">
-        <v>4.360823244986695</v>
+        <v>4.618127414174666</v>
       </c>
       <c r="G11">
-        <v>-4.306362098697833</v>
+        <v>-1.40947253510412</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.4110803341642</v>
       </c>
       <c r="E12">
-        <v>-22.88016681367617</v>
+        <v>-21.72075972738836</v>
       </c>
       <c r="F12">
-        <v>4.786037486722126</v>
+        <v>5.022889264734977</v>
       </c>
       <c r="G12">
-        <v>-4.160760995335147</v>
+        <v>-0.3666871062346284</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.78389236970736</v>
       </c>
       <c r="E13">
-        <v>-23.18395949248073</v>
+        <v>-22.34028214248171</v>
       </c>
       <c r="F13">
-        <v>4.994237693006948</v>
+        <v>5.142967746709988</v>
       </c>
       <c r="G13">
-        <v>-3.228676898753344</v>
+        <v>-0.18416679901799</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.08975551904182</v>
       </c>
       <c r="E14">
-        <v>-23.38671738770017</v>
+        <v>-24.53667807720798</v>
       </c>
       <c r="F14">
-        <v>5.272320630126742</v>
+        <v>5.308265148469018</v>
       </c>
       <c r="G14">
-        <v>-3.108666312409225</v>
+        <v>0.7003877952564962</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.31240169909375</v>
       </c>
       <c r="E15">
-        <v>-25.47489637906514</v>
+        <v>-25.04830054212056</v>
       </c>
       <c r="F15">
-        <v>5.209387901801258</v>
+        <v>5.669348842614517</v>
       </c>
       <c r="G15">
-        <v>-3.017907706450105</v>
+        <v>1.022930936602149</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.46770299185049</v>
       </c>
       <c r="E16">
-        <v>-26.85450504244993</v>
+        <v>-26.19757290357921</v>
       </c>
       <c r="F16">
-        <v>5.598317994559265</v>
+        <v>5.848528025309661</v>
       </c>
       <c r="G16">
-        <v>-1.960800857577726</v>
+        <v>1.518460014011338</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.55001177047157</v>
       </c>
       <c r="E17">
-        <v>-26.91781310907716</v>
+        <v>-26.82506543292606</v>
       </c>
       <c r="F17">
-        <v>5.914444533020029</v>
+        <v>6.358509103373565</v>
       </c>
       <c r="G17">
-        <v>-1.73016839203886</v>
+        <v>1.898556989557221</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.58735134823368</v>
       </c>
       <c r="E18">
-        <v>-27.95988743382623</v>
+        <v>-28.03285926398583</v>
       </c>
       <c r="F18">
-        <v>5.577628690306945</v>
+        <v>6.458753156255945</v>
       </c>
       <c r="G18">
-        <v>-0.9785851698947398</v>
+        <v>1.640347679676225</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.596118358703277</v>
       </c>
       <c r="E19">
-        <v>-27.86668691027437</v>
+        <v>-28.48323864641868</v>
       </c>
       <c r="F19">
-        <v>6.316353486245099</v>
+        <v>6.600312861720353</v>
       </c>
       <c r="G19">
-        <v>-0.6804937179021442</v>
+        <v>2.869096383123197</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.619551516979056</v>
       </c>
       <c r="E20">
-        <v>-29.27780469580453</v>
+        <v>-28.68385457343249</v>
       </c>
       <c r="F20">
-        <v>6.499523743086931</v>
+        <v>7.116529889592532</v>
       </c>
       <c r="G20">
-        <v>-0.9352666815133762</v>
+        <v>3.524269898072662</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.691192261150597</v>
       </c>
       <c r="E21">
-        <v>-30.20377800394495</v>
+        <v>-29.73212158638705</v>
       </c>
       <c r="F21">
-        <v>6.406191587813511</v>
+        <v>7.529015437816546</v>
       </c>
       <c r="G21">
-        <v>-0.4271575310549559</v>
+        <v>3.355660503212041</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.854339784955432</v>
       </c>
       <c r="E22">
-        <v>-30.59750164806784</v>
+        <v>-30.42357654685524</v>
       </c>
       <c r="F22">
-        <v>6.428893824854634</v>
+        <v>7.612241510775812</v>
       </c>
       <c r="G22">
-        <v>-0.2278196524988199</v>
+        <v>3.298937615942168</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.1394510113221</v>
       </c>
       <c r="E23">
-        <v>-30.41593021849329</v>
+        <v>-29.48643602181191</v>
       </c>
       <c r="F23">
-        <v>7.168446988195588</v>
+        <v>7.479177541394516</v>
       </c>
       <c r="G23">
-        <v>0.6446249661930123</v>
+        <v>4.161741926023643</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.566689434224614</v>
       </c>
       <c r="E24">
-        <v>-30.99967995316305</v>
+        <v>-30.64616689399127</v>
       </c>
       <c r="F24">
-        <v>6.86533575836761</v>
+        <v>7.316618722269141</v>
       </c>
       <c r="G24">
-        <v>0.1864487741034193</v>
+        <v>4.987352256971405</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.147429082606115</v>
       </c>
       <c r="E25">
-        <v>-31.44617390489733</v>
+        <v>-31.04678966826484</v>
       </c>
       <c r="F25">
-        <v>7.270998872662167</v>
+        <v>7.415381654235315</v>
       </c>
       <c r="G25">
-        <v>1.125799518143922</v>
+        <v>3.807520174412705</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.870704173819992</v>
       </c>
       <c r="E26">
-        <v>-31.55521503052802</v>
+        <v>-30.64180823775888</v>
       </c>
       <c r="F26">
-        <v>6.792447710595281</v>
+        <v>6.929032241438475</v>
       </c>
       <c r="G26">
-        <v>0.9061779270686717</v>
+        <v>4.22743639170494</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.728236038735822</v>
       </c>
       <c r="E27">
-        <v>-30.4048377214115</v>
+        <v>-30.30853972163839</v>
       </c>
       <c r="F27">
-        <v>6.503542981725315</v>
+        <v>7.140259302213126</v>
       </c>
       <c r="G27">
-        <v>1.039334689749237</v>
+        <v>3.600478656386684</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.6862452510076</v>
       </c>
       <c r="E28">
-        <v>-31.29897132880399</v>
+        <v>-31.71474184863322</v>
       </c>
       <c r="F28">
-        <v>6.428588985650404</v>
+        <v>7.345828613626657</v>
       </c>
       <c r="G28">
-        <v>0.5410082013593634</v>
+        <v>4.416690348548456</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.725173141208888</v>
       </c>
       <c r="E29">
-        <v>-31.25858413336658</v>
+        <v>-31.02453221851714</v>
       </c>
       <c r="F29">
-        <v>6.568927677563085</v>
+        <v>7.149242118329084</v>
       </c>
       <c r="G29">
-        <v>-0.1377463294663295</v>
+        <v>3.262634173558521</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.807279576014684</v>
       </c>
       <c r="E30">
-        <v>-30.57204709567072</v>
+        <v>-30.68140747871896</v>
       </c>
       <c r="F30">
-        <v>6.255710365420953</v>
+        <v>7.156299808600936</v>
       </c>
       <c r="G30">
-        <v>0.5207443521134846</v>
+        <v>3.540554471580337</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.915030981605911</v>
       </c>
       <c r="E31">
-        <v>-30.85777116318468</v>
+        <v>-29.78385713768768</v>
       </c>
       <c r="F31">
-        <v>6.441425366924185</v>
+        <v>7.330376248094836</v>
       </c>
       <c r="G31">
-        <v>-0.04509078091320748</v>
+        <v>2.982840106761477</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.02309368017665</v>
       </c>
       <c r="E32">
-        <v>-31.01895313853969</v>
+        <v>-30.08178091417831</v>
       </c>
       <c r="F32">
-        <v>6.656320438558433</v>
+        <v>6.805516034741846</v>
       </c>
       <c r="G32">
-        <v>0.1094123794045788</v>
+        <v>3.231822926224523</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.126667043540787</v>
       </c>
       <c r="E33">
-        <v>-28.85099602058159</v>
+        <v>-29.64302386028614</v>
       </c>
       <c r="F33">
-        <v>6.502585389007678</v>
+        <v>7.009287788891302</v>
       </c>
       <c r="G33">
-        <v>-0.3838622164923673</v>
+        <v>3.14798667098802</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.215770917861666</v>
       </c>
       <c r="E34">
-        <v>-29.95936267632895</v>
+        <v>-29.18219955255459</v>
       </c>
       <c r="F34">
-        <v>6.566916401509088</v>
+        <v>6.67740238895968</v>
       </c>
       <c r="G34">
-        <v>-0.2685426731773948</v>
+        <v>3.00013108611309</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.295658757768974</v>
       </c>
       <c r="E35">
-        <v>-28.89359084709774</v>
+        <v>-28.1310818652122</v>
       </c>
       <c r="F35">
-        <v>6.600604447046138</v>
+        <v>7.133445151957698</v>
       </c>
       <c r="G35">
-        <v>-1.047729224027958</v>
+        <v>2.482656402324072</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.363133371382007</v>
       </c>
       <c r="E36">
-        <v>-28.5576958160528</v>
+        <v>-28.73791096766205</v>
       </c>
       <c r="F36">
-        <v>6.223688995098335</v>
+        <v>7.172098431707128</v>
       </c>
       <c r="G36">
-        <v>-1.839201209374756</v>
+        <v>2.344285530419154</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.424626929228928</v>
       </c>
       <c r="E37">
-        <v>-28.21759383265474</v>
+        <v>-28.52660331351614</v>
       </c>
       <c r="F37">
-        <v>6.597869177882094</v>
+        <v>6.839523830096377</v>
       </c>
       <c r="G37">
-        <v>-1.246779085122177</v>
+        <v>2.408152574962774</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.480452369964975</v>
       </c>
       <c r="E38">
-        <v>-27.73870317786958</v>
+        <v>-26.19692986027012</v>
       </c>
       <c r="F38">
-        <v>6.352427229902212</v>
+        <v>7.372762151361281</v>
       </c>
       <c r="G38">
-        <v>-1.240810171514871</v>
+        <v>1.593874241395936</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.536784954568549</v>
       </c>
       <c r="E39">
-        <v>-27.06469416351595</v>
+        <v>-25.46741534000446</v>
       </c>
       <c r="F39">
-        <v>6.979893999970365</v>
+        <v>7.238117656975443</v>
       </c>
       <c r="G39">
-        <v>-1.568620390813504</v>
+        <v>1.866729404742667</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.59866591340711</v>
       </c>
       <c r="E40">
-        <v>-26.00263115449702</v>
+        <v>-25.8749780006948</v>
       </c>
       <c r="F40">
-        <v>6.565148665471513</v>
+        <v>7.224698105050091</v>
       </c>
       <c r="G40">
-        <v>-1.796988443203509</v>
+        <v>0.9059561205175406</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.669192217225312</v>
       </c>
       <c r="E41">
-        <v>-26.12602754273203</v>
+        <v>-25.67763163191453</v>
       </c>
       <c r="F41">
-        <v>7.121856291992533</v>
+        <v>7.199172791900227</v>
       </c>
       <c r="G41">
-        <v>-2.021009749300451</v>
+        <v>2.319128694866232</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.754054946145487</v>
       </c>
       <c r="E42">
-        <v>-26.41996173362189</v>
+        <v>-25.06527326270131</v>
       </c>
       <c r="F42">
-        <v>6.792668056324426</v>
+        <v>6.897438308695702</v>
       </c>
       <c r="G42">
-        <v>-1.551087741637524</v>
+        <v>1.989163310421534</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.851145023125149</v>
       </c>
       <c r="E43">
-        <v>-24.57305078043758</v>
+        <v>-24.8279314114853</v>
       </c>
       <c r="F43">
-        <v>7.082568482812557</v>
+        <v>7.377483845557237</v>
       </c>
       <c r="G43">
-        <v>-2.34298016626781</v>
+        <v>1.692194133366751</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.966075631459416</v>
       </c>
       <c r="E44">
-        <v>-24.6019288591845</v>
+        <v>-24.29734369742859</v>
       </c>
       <c r="F44">
-        <v>7.099548357835141</v>
+        <v>7.213607922261412</v>
       </c>
       <c r="G44">
-        <v>-2.530664924525711</v>
+        <v>1.088132130998095</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.092596711771456</v>
       </c>
       <c r="E45">
-        <v>-23.83763565853993</v>
+        <v>-22.52529294806508</v>
       </c>
       <c r="F45">
-        <v>7.116836385531568</v>
+        <v>7.427505639542688</v>
       </c>
       <c r="G45">
-        <v>-2.385120100437192</v>
+        <v>0.7411538530270816</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.235717335599787</v>
       </c>
       <c r="E46">
-        <v>-22.99353263198419</v>
+        <v>-22.34494647070961</v>
       </c>
       <c r="F46">
-        <v>7.100380038707552</v>
+        <v>7.393002480481283</v>
       </c>
       <c r="G46">
-        <v>-2.906918356700499</v>
+        <v>1.309058077015818</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.387475852151608</v>
       </c>
       <c r="E47">
-        <v>-22.72251251957313</v>
+        <v>-21.88099978014977</v>
       </c>
       <c r="F47">
-        <v>7.130101861119999</v>
+        <v>7.622163695526544</v>
       </c>
       <c r="G47">
-        <v>-2.231610103781188</v>
+        <v>0.7138683366924085</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.554184469171449</v>
       </c>
       <c r="E48">
-        <v>-21.39993998631495</v>
+        <v>-21.6380743204823</v>
       </c>
       <c r="F48">
-        <v>7.142840495040249</v>
+        <v>7.681300844412401</v>
       </c>
       <c r="G48">
-        <v>-2.655128194620151</v>
+        <v>0.5187050560612935</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.727887981037213</v>
       </c>
       <c r="E49">
-        <v>-21.72462704419091</v>
+        <v>-20.56788270061961</v>
       </c>
       <c r="F49">
-        <v>7.377692594142743</v>
+        <v>7.614088770084055</v>
       </c>
       <c r="G49">
-        <v>-2.855508895021157</v>
+        <v>-0.1215147246872828</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.916568467238402</v>
       </c>
       <c r="E50">
-        <v>-21.64605802015783</v>
+        <v>-20.67600001755273</v>
       </c>
       <c r="F50">
-        <v>7.428299215514571</v>
+        <v>7.595526713322124</v>
       </c>
       <c r="G50">
-        <v>-2.511390928396074</v>
+        <v>-0.06709928765828234</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.114248644909202</v>
       </c>
       <c r="E51">
-        <v>-20.44304172917615</v>
+        <v>-20.37330775793203</v>
       </c>
       <c r="F51">
-        <v>7.285266672807985</v>
+        <v>7.723363684391755</v>
       </c>
       <c r="G51">
-        <v>-3.13394232760156</v>
+        <v>-0.3613273330065483</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.329058714220101</v>
       </c>
       <c r="E52">
-        <v>-20.18388169019118</v>
+        <v>-19.14951482820317</v>
       </c>
       <c r="F52">
-        <v>7.224726269541787</v>
+        <v>7.770698254522523</v>
       </c>
       <c r="G52">
-        <v>-3.338186434646896</v>
+        <v>-0.5019593075147883</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.558756740743048</v>
       </c>
       <c r="E53">
-        <v>-19.79599072059017</v>
+        <v>-19.01913553304833</v>
       </c>
       <c r="F53">
-        <v>7.358757772049552</v>
+        <v>7.921911753699157</v>
       </c>
       <c r="G53">
-        <v>-3.430825430472322</v>
+        <v>-1.174347659268463</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.806044007501919</v>
       </c>
       <c r="E54">
-        <v>-19.87085998135899</v>
+        <v>-18.53273666835846</v>
       </c>
       <c r="F54">
-        <v>7.304640529624661</v>
+        <v>7.512164788108798</v>
       </c>
       <c r="G54">
-        <v>-4.215663082558421</v>
+        <v>-1.376959667362938</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.070390541236142</v>
       </c>
       <c r="E55">
-        <v>-19.48970738108138</v>
+        <v>-17.91001262214169</v>
       </c>
       <c r="F55">
-        <v>7.429922815624058</v>
+        <v>7.399326237234255</v>
       </c>
       <c r="G55">
-        <v>-4.516883000085627</v>
+        <v>-1.771169498542733</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.346107346760331</v>
       </c>
       <c r="E56">
-        <v>-18.8735903784418</v>
+        <v>-17.4529401551255</v>
       </c>
       <c r="F56">
-        <v>7.11503220132827</v>
+        <v>7.829825462999547</v>
       </c>
       <c r="G56">
-        <v>-5.081264803620579</v>
+        <v>-2.257756792450352</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.634361936950584</v>
       </c>
       <c r="E57">
-        <v>-17.98033982348081</v>
+        <v>-15.99530135611454</v>
       </c>
       <c r="F57">
-        <v>7.237241244263282</v>
+        <v>7.740799161485878</v>
       </c>
       <c r="G57">
-        <v>-4.83760865193022</v>
+        <v>-2.440038740388162</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.924594477200257</v>
       </c>
       <c r="E58">
-        <v>-18.43267097821097</v>
+        <v>-16.31565466436516</v>
       </c>
       <c r="F58">
-        <v>7.53342566586905</v>
+        <v>7.516969319045035</v>
       </c>
       <c r="G58">
-        <v>-4.933958769305169</v>
+        <v>-2.350326266819452</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.219525071288503</v>
       </c>
       <c r="E59">
-        <v>-17.11888821300168</v>
+        <v>-14.78118577534006</v>
       </c>
       <c r="F59">
-        <v>6.954416732129863</v>
+        <v>7.606232533635905</v>
       </c>
       <c r="G59">
-        <v>-5.398696462653597</v>
+        <v>-2.151650497371171</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.506079333384802</v>
       </c>
       <c r="E60">
-        <v>-16.7184397849774</v>
+        <v>-15.61215622727357</v>
       </c>
       <c r="F60">
-        <v>7.230375735228879</v>
+        <v>7.294269369741611</v>
       </c>
       <c r="G60">
-        <v>-6.144794110839144</v>
+        <v>-2.496589479289993</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.789032219888096</v>
       </c>
       <c r="E61">
-        <v>-16.30326475948017</v>
+        <v>-14.69423454591878</v>
       </c>
       <c r="F61">
-        <v>7.100351874215858</v>
+        <v>7.696143531535762</v>
       </c>
       <c r="G61">
-        <v>-5.583904932848124</v>
+        <v>-3.901482379244967</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.055012912515034</v>
       </c>
       <c r="E62">
-        <v>-16.52995563983014</v>
+        <v>-15.44068103049912</v>
       </c>
       <c r="F62">
-        <v>7.019551261011988</v>
+        <v>7.382089568316803</v>
       </c>
       <c r="G62">
-        <v>-6.38560319336573</v>
+        <v>-3.392065563298535</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.310614516816957</v>
       </c>
       <c r="E63">
-        <v>-16.51922315643196</v>
+        <v>-13.64635924596589</v>
       </c>
       <c r="F63">
-        <v>7.085371678103631</v>
+        <v>7.505688611753712</v>
       </c>
       <c r="G63">
-        <v>-6.438763933635347</v>
+        <v>-3.549955411702995</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.542603695050285</v>
       </c>
       <c r="E64">
-        <v>-16.33829703440351</v>
+        <v>-13.64056279923607</v>
       </c>
       <c r="F64">
-        <v>6.943427610164325</v>
+        <v>7.233170646845925</v>
       </c>
       <c r="G64">
-        <v>-6.415126638484951</v>
+        <v>-4.095784918035871</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.756319415931106</v>
       </c>
       <c r="E65">
-        <v>-16.2048655477675</v>
+        <v>-14.26365818032147</v>
       </c>
       <c r="F65">
-        <v>6.882792773014207</v>
+        <v>7.035868442112332</v>
       </c>
       <c r="G65">
-        <v>-6.504974844420771</v>
+        <v>-3.371391206405786</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.940251975918454</v>
       </c>
       <c r="E66">
-        <v>-15.18083719193899</v>
+        <v>-14.35008863523187</v>
       </c>
       <c r="F66">
-        <v>6.967789895480658</v>
+        <v>7.15434817499994</v>
       </c>
       <c r="G66">
-        <v>-7.328403525858154</v>
+        <v>-4.32672526430989</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.0949228079116</v>
       </c>
       <c r="E67">
-        <v>-14.42102265208802</v>
+        <v>-13.7741844817804</v>
       </c>
       <c r="F67">
-        <v>6.744592925735554</v>
+        <v>6.838526475743406</v>
       </c>
       <c r="G67">
-        <v>-6.885167825787292</v>
+        <v>-3.810746947104622</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.21333930925898</v>
       </c>
       <c r="E68">
-        <v>-15.58043879532384</v>
+        <v>-13.05831878217386</v>
       </c>
       <c r="F68">
-        <v>6.791823121573571</v>
+        <v>7.120206184126156</v>
       </c>
       <c r="G68">
-        <v>-6.993300174736507</v>
+        <v>-4.588327883368639</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.28945004529607</v>
       </c>
       <c r="E69">
-        <v>-14.13699223385292</v>
+        <v>-11.05080549830752</v>
       </c>
       <c r="F69">
-        <v>6.495628759558968</v>
+        <v>6.827005541905271</v>
       </c>
       <c r="G69">
-        <v>-6.738931097681066</v>
+        <v>-4.723633190104191</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.32305925635162</v>
       </c>
       <c r="E70">
-        <v>-13.20106081136964</v>
+        <v>-13.00630020124775</v>
       </c>
       <c r="F70">
-        <v>6.738052136723049</v>
+        <v>6.679604189516321</v>
       </c>
       <c r="G70">
-        <v>-7.04393165821412</v>
+        <v>-4.07239922434646</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.30461999843738</v>
       </c>
       <c r="E71">
-        <v>-14.78184240407118</v>
+        <v>-13.01556545906744</v>
       </c>
       <c r="F71">
-        <v>6.627531357841539</v>
+        <v>6.192232571344427</v>
       </c>
       <c r="G71">
-        <v>-7.17497960338617</v>
+        <v>-3.676133544386778</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.24202858052228</v>
       </c>
       <c r="E72">
-        <v>-14.54755727281034</v>
+        <v>-12.14047861335122</v>
       </c>
       <c r="F72">
-        <v>6.285417277220149</v>
+        <v>5.998928067696745</v>
       </c>
       <c r="G72">
-        <v>-6.847093241540134</v>
+        <v>-4.046305504405924</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.12692263196475</v>
       </c>
       <c r="E73">
-        <v>-14.49275820884352</v>
+        <v>-12.67002477838617</v>
       </c>
       <c r="F73">
-        <v>6.297084003721177</v>
+        <v>6.161616112136957</v>
       </c>
       <c r="G73">
-        <v>-7.49240133078257</v>
+        <v>-3.85118526086682</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.969593693962253</v>
       </c>
       <c r="E74">
-        <v>-14.39980222288807</v>
+        <v>-12.81918365525081</v>
       </c>
       <c r="F74">
-        <v>6.172350096942433</v>
+        <v>6.158980247061248</v>
       </c>
       <c r="G74">
-        <v>-6.773820937119445</v>
+        <v>-3.495675707041105</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.762282921910868</v>
       </c>
       <c r="E75">
-        <v>-14.96509163326556</v>
+        <v>-13.64938426660301</v>
       </c>
       <c r="F75">
-        <v>6.059377350548636</v>
+        <v>6.4070464629732</v>
       </c>
       <c r="G75">
-        <v>-7.13982160975911</v>
+        <v>-3.772937206500606</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.515206700093572</v>
       </c>
       <c r="E76">
-        <v>-14.3684108410669</v>
+        <v>-12.48671215055567</v>
       </c>
       <c r="F76">
-        <v>6.12943238180339</v>
+        <v>5.952120339234156</v>
       </c>
       <c r="G76">
-        <v>-7.272203704783487</v>
+        <v>-3.837386907059138</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.222747635849862</v>
       </c>
       <c r="E77">
-        <v>-15.06487202955057</v>
+        <v>-13.09123625973562</v>
       </c>
       <c r="F77">
-        <v>5.995430700522125</v>
+        <v>6.226961046339393</v>
       </c>
       <c r="G77">
-        <v>-6.451648576874191</v>
+        <v>-3.316899626829382</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.89473966408868</v>
       </c>
       <c r="E78">
-        <v>-14.74907436615167</v>
+        <v>-13.55967972498507</v>
       </c>
       <c r="F78">
-        <v>6.138067283610172</v>
+        <v>5.453807644406086</v>
       </c>
       <c r="G78">
-        <v>-6.620989602298991</v>
+        <v>-2.996435508082392</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.528868445829595</v>
       </c>
       <c r="E79">
-        <v>-15.37695181578917</v>
+        <v>-14.55858863549303</v>
       </c>
       <c r="F79">
-        <v>5.89587419258407</v>
+        <v>6.162073370943302</v>
       </c>
       <c r="G79">
-        <v>-6.359691553429855</v>
+        <v>-2.465788163592614</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.131996303277477</v>
       </c>
       <c r="E80">
-        <v>-15.78652964741292</v>
+        <v>-14.66009890884897</v>
       </c>
       <c r="F80">
-        <v>5.648187368942601</v>
+        <v>5.920647348132192</v>
       </c>
       <c r="G80">
-        <v>-5.837029244780799</v>
+        <v>-2.290537814380215</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.706622534566082</v>
       </c>
       <c r="E81">
-        <v>-17.11596281879272</v>
+        <v>-14.94814608352886</v>
       </c>
       <c r="F81">
-        <v>5.605867735068379</v>
+        <v>5.671534075823102</v>
       </c>
       <c r="G81">
-        <v>-5.980236823718592</v>
+        <v>-1.492775792508801</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.256271721492809</v>
       </c>
       <c r="E82">
-        <v>-17.6341334571204</v>
+        <v>-15.5218448701386</v>
       </c>
       <c r="F82">
-        <v>5.630884430632925</v>
+        <v>5.544197438664762</v>
       </c>
       <c r="G82">
-        <v>-5.768593647392985</v>
+        <v>-1.876047581226844</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.789706398038476</v>
       </c>
       <c r="E83">
-        <v>-18.35724018666521</v>
+        <v>-15.45634502209165</v>
       </c>
       <c r="F83">
-        <v>5.757707480001529</v>
+        <v>5.312947081029641</v>
       </c>
       <c r="G83">
-        <v>-5.682049365905358</v>
+        <v>-1.591241348483344</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.306774384462032</v>
       </c>
       <c r="E84">
-        <v>-19.34076587096911</v>
+        <v>-17.19046980164092</v>
       </c>
       <c r="F84">
-        <v>5.717496869534836</v>
+        <v>5.629848971379426</v>
       </c>
       <c r="G84">
-        <v>-5.18673878450176</v>
+        <v>-1.444110773081515</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.820459855500069</v>
       </c>
       <c r="E85">
-        <v>-19.5475722219514</v>
+        <v>-18.21330716880541</v>
       </c>
       <c r="F85">
-        <v>5.39675963811009</v>
+        <v>5.73640021366672</v>
       </c>
       <c r="G85">
-        <v>-4.578614742756417</v>
+        <v>-1.124206136530661</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.328021037536055</v>
       </c>
       <c r="E86">
-        <v>-20.0372995150369</v>
+        <v>-18.73990529726137</v>
       </c>
       <c r="F86">
-        <v>5.559121305793598</v>
+        <v>5.388918312275189</v>
       </c>
       <c r="G86">
-        <v>-4.37778380816207</v>
+        <v>-0.517495697730588</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.8436056506213</v>
       </c>
       <c r="E87">
-        <v>-21.95745853529528</v>
+        <v>-19.7288243941084</v>
       </c>
       <c r="F87">
-        <v>5.419170289825427</v>
+        <v>5.250774793979927</v>
       </c>
       <c r="G87">
-        <v>-4.527778005455369</v>
+        <v>-0.2392940033379339</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.365914752457575</v>
       </c>
       <c r="E88">
-        <v>-23.16389382415275</v>
+        <v>-20.4711771381858</v>
       </c>
       <c r="F88">
-        <v>5.37038939020937</v>
+        <v>5.286896582946402</v>
       </c>
       <c r="G88">
-        <v>-3.619172297838078</v>
+        <v>-0.4466698864634203</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.907929361561147</v>
       </c>
       <c r="E89">
-        <v>-24.71171718302646</v>
+        <v>-23.00656105170425</v>
       </c>
       <c r="F89">
-        <v>5.344917092573285</v>
+        <v>4.667420244845654</v>
       </c>
       <c r="G89">
-        <v>-4.058206915619604</v>
+        <v>-0.3204983748707168</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.469794691491815</v>
       </c>
       <c r="E90">
-        <v>-26.14716193092582</v>
+        <v>-24.28490850780353</v>
       </c>
       <c r="F90">
-        <v>4.881087675988952</v>
+        <v>5.100258780156451</v>
       </c>
       <c r="G90">
-        <v>-3.41093567287238</v>
+        <v>0.8271552050462685</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.062128091412948</v>
       </c>
       <c r="E91">
-        <v>-27.39816646096678</v>
+        <v>-26.82511071766614</v>
       </c>
       <c r="F91">
-        <v>4.98284929795326</v>
+        <v>4.816821276144961</v>
       </c>
       <c r="G91">
-        <v>-3.384097080185509</v>
+        <v>0.3925401655596685</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.686887931609985</v>
       </c>
       <c r="E92">
-        <v>-29.39593899724262</v>
+        <v>-27.46736607227799</v>
       </c>
       <c r="F92">
-        <v>4.889657965138316</v>
+        <v>4.58031575570648</v>
       </c>
       <c r="G92">
-        <v>-2.774178722757882</v>
+        <v>0.474800601119479</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.352591758522554</v>
       </c>
       <c r="E93">
-        <v>-31.10047925609978</v>
+        <v>-29.01612229679729</v>
       </c>
       <c r="F93">
-        <v>4.251680869463443</v>
+        <v>4.382326006028564</v>
       </c>
       <c r="G93">
-        <v>-2.954785534652821</v>
+        <v>0.5917058957477624</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.062678854566413</v>
       </c>
       <c r="E94">
-        <v>-33.66077883360843</v>
+        <v>-31.46748037510341</v>
       </c>
       <c r="F94">
-        <v>4.243801438728014</v>
+        <v>4.176365705200912</v>
       </c>
       <c r="G94">
-        <v>-2.941331477581223</v>
+        <v>1.651815409424261</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.821378643692769</v>
       </c>
       <c r="E95">
-        <v>-35.60732300767251</v>
+        <v>-33.05014581299214</v>
       </c>
       <c r="F95">
-        <v>3.770737382337273</v>
+        <v>4.024574005577125</v>
       </c>
       <c r="G95">
-        <v>-2.568352174944774</v>
+        <v>0.8481837903117191</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.635191899795948</v>
       </c>
       <c r="E96">
-        <v>-37.13544976884985</v>
+        <v>-35.63859212069547</v>
       </c>
       <c r="F96">
-        <v>3.870598729479559</v>
+        <v>3.635865915283068</v>
       </c>
       <c r="G96">
-        <v>-2.149885976598739</v>
+        <v>0.6409204657345678</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.499795710759479</v>
       </c>
       <c r="E97">
-        <v>-39.46020756356054</v>
+        <v>-37.76171508174063</v>
       </c>
       <c r="F97">
-        <v>2.898670285570482</v>
+        <v>2.947167883534782</v>
       </c>
       <c r="G97">
-        <v>-2.642925523762397</v>
+        <v>0.6282245235914629</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.425861775142234</v>
       </c>
       <c r="E98">
-        <v>-42.65637961156724</v>
+        <v>-40.44844738930643</v>
       </c>
       <c r="F98">
-        <v>2.61652834817697</v>
+        <v>2.99768007102269</v>
       </c>
       <c r="G98">
-        <v>-3.186431027126705</v>
+        <v>0.9181389281020585</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.397024328589118</v>
       </c>
       <c r="E99">
-        <v>-45.14603952303024</v>
+        <v>-42.33073930991267</v>
       </c>
       <c r="F99">
-        <v>2.267033513996636</v>
+        <v>2.700094051771385</v>
       </c>
       <c r="G99">
-        <v>-3.048702401056406</v>
+        <v>0.5676945089514285</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.435247597317482</v>
       </c>
       <c r="E100">
-        <v>-47.17645103571636</v>
+        <v>-45.0097528335324</v>
       </c>
       <c r="F100">
-        <v>2.384358502724742</v>
+        <v>2.0862588956837</v>
       </c>
       <c r="G100">
-        <v>-2.805774569384686</v>
+        <v>1.051553913334687</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.505944157041522</v>
       </c>
       <c r="E101">
-        <v>-49.15616288553111</v>
+        <v>-47.78701612922254</v>
       </c>
       <c r="F101">
-        <v>1.64648361174186</v>
+        <v>1.869051022260836</v>
       </c>
       <c r="G101">
-        <v>-2.974033046418144</v>
+        <v>1.095263046089685</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.66579322337704</v>
       </c>
       <c r="E102">
-        <v>-52.27761398029275</v>
+        <v>-50.21626619742322</v>
       </c>
       <c r="F102">
-        <v>1.255683065388331</v>
+        <v>1.600191127803812</v>
       </c>
       <c r="G102">
-        <v>-2.442369364447809</v>
+        <v>1.109968489375128</v>
       </c>
     </row>
   </sheetData>
